--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>3</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>5</v>
-      </c>
       <c r="E16" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
         <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>63.636363636363</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L16" s="14">
-        <v>20</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M16" s="14">
-        <v>125</v>
+        <v>137.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-81.443298969072</v>
+        <v>-84.297520661157</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J17" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K17" s="14">
-        <v>162.5</v>
+        <v>160</v>
       </c>
       <c r="L17" s="14">
-        <v>110</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M17" s="14">
-        <v>200</v>
+        <v>188.888888888889</v>
       </c>
       <c r="N17" s="14">
-        <v>31.25</v>
+        <v>36.842105263157</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-50</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>-31.578947368421</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L18" s="14">
-        <v>-40.909090909090</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="14">
-        <v>-40.909090909090</v>
+        <v>-44</v>
       </c>
       <c r="N18" s="14">
-        <v>-86.458333333333</v>
+        <v>-86.538461538461</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E19" s="14">
-        <v>-10.714285714285</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F19" s="15">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G19" s="15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19" s="14">
-        <v>3.260869565217</v>
+        <v>-6</v>
       </c>
       <c r="I19" s="15">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="J19" s="15">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="K19" s="14">
-        <v>5.691056910569</v>
+        <v>-1.282051282051</v>
       </c>
       <c r="L19" s="14">
-        <v>30</v>
+        <v>25.203252032520</v>
       </c>
       <c r="M19" s="14">
-        <v>17.117117117117</v>
+        <v>15.789473684210</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.053763440860</v>
+        <v>-64.018691588785</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>21</v>
+        <v>33.333333333333</v>
+      </c>
+      <c r="M20" s="14">
+        <v>100</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.130841121495</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.666666666666</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="F21" s="17">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.875968992248</v>
+        <v>-8.759124087591</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="K21" s="18">
-        <v>9.523809523809</v>
+        <v>3.827751196172</v>
       </c>
       <c r="L21" s="18">
-        <v>20.261437908496</v>
+        <v>15.425531914893</v>
       </c>
       <c r="M21" s="18">
-        <v>24.324324324324</v>
+        <v>22.598870056497</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.294629898403</v>
+        <v>-72.772898368883</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="15">
         <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-71.428571428571</v>
+        <v>-70</v>
       </c>
       <c r="L22" s="14">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="M22" s="14">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="15">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.941176470588</v>
+        <v>-31.506849315068</v>
       </c>
       <c r="F24" s="15">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G24" s="15">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.413284132841</v>
+        <v>-29.924242424242</v>
       </c>
       <c r="I24" s="15">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="J24" s="15">
-        <v>368</v>
+        <v>441</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.467391304347</v>
+        <v>-23.129251700680</v>
       </c>
       <c r="L24" s="14">
-        <v>-30.528846153846</v>
+        <v>-30.816326530612</v>
       </c>
       <c r="M24" s="14">
-        <v>80.625</v>
+        <v>88.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D25" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E25" s="14">
-        <v>-31.428571428571</v>
+        <v>-37.179487179487</v>
       </c>
       <c r="F25" s="15">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G25" s="15">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H25" s="14">
-        <v>-24.528301886792</v>
+        <v>-30.597014925373</v>
       </c>
       <c r="I25" s="15">
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="J25" s="15">
-        <v>362</v>
+        <v>440</v>
       </c>
       <c r="K25" s="14">
-        <v>-17.403314917127</v>
+        <v>-20.681818181818</v>
       </c>
       <c r="L25" s="14">
-        <v>-27.602905569007</v>
+        <v>-28.629856850715</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>-42.857142857142</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="I26" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J26" s="15">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K26" s="14">
-        <v>-34.693877551020</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="L26" s="14">
-        <v>6.666666666666</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="M26" s="14">
-        <v>33.333333333333</v>
+        <v>34.482758620689</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>3</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>80</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1566,14 +1566,14 @@
       <c r="H31" s="14">
         <v>-100</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>1</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -943,31 +943,31 @@
         <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>46.153846153846</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>137.5</v>
+        <v>150</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.297520661157</v>
+        <v>-85.815602836879</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>111.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K17" s="14">
-        <v>160</v>
+        <v>153.846153846154</v>
       </c>
       <c r="L17" s="14">
-        <v>85.714285714285</v>
+        <v>65</v>
       </c>
       <c r="M17" s="14">
-        <v>188.888888888889</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>36.842105263157</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-58.823529411764</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-36.363636363636</v>
+        <v>-24</v>
       </c>
       <c r="L18" s="14">
-        <v>-46.153846153846</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="M18" s="14">
-        <v>-44</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="N18" s="14">
-        <v>-86.538461538461</v>
+        <v>-84.677419354838</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E19" s="14">
-        <v>-27.272727272727</v>
+        <v>-18.75</v>
       </c>
       <c r="F19" s="15">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G19" s="15">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H19" s="14">
-        <v>-6</v>
+        <v>-7.608695652173</v>
       </c>
       <c r="I19" s="15">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="J19" s="15">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.282051282051</v>
+        <v>-2.906976744186</v>
       </c>
       <c r="L19" s="14">
-        <v>25.203252032520</v>
+        <v>17.605633802816</v>
       </c>
       <c r="M19" s="14">
-        <v>15.789473684210</v>
+        <v>9.868421052631</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.018691588785</v>
+        <v>-65.424430641821</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
       </c>
       <c r="K20" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.774193548387</v>
+        <v>-95.620437956204</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.951219512195</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.759124087591</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="J21" s="17">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="K21" s="18">
-        <v>3.827751196172</v>
+        <v>5.150214592274</v>
       </c>
       <c r="L21" s="18">
-        <v>15.425531914893</v>
+        <v>8.888888888888</v>
       </c>
       <c r="M21" s="18">
-        <v>22.598870056497</v>
+        <v>19.512195121951</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.772898368883</v>
+        <v>-73.076923076923</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1201,16 +1201,16 @@
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K22" s="14">
+        <v>-75</v>
+      </c>
+      <c r="L22" s="14">
         <v>-70</v>
       </c>
-      <c r="L22" s="14">
-        <v>-62.5</v>
-      </c>
       <c r="M22" s="14">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D24" s="15">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" s="14">
-        <v>-31.506849315068</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="15">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G24" s="15">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.924242424242</v>
+        <v>-35.531135531135</v>
       </c>
       <c r="I24" s="15">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="J24" s="15">
-        <v>441</v>
+        <v>513</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.129251700680</v>
+        <v>-26.900584795321</v>
       </c>
       <c r="L24" s="14">
-        <v>-30.816326530612</v>
+        <v>-34.440559440559</v>
       </c>
       <c r="M24" s="14">
-        <v>88.333333333333</v>
+        <v>80.288461538461</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D25" s="15">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E25" s="14">
-        <v>-37.179487179487</v>
+        <v>-62.318840579710</v>
       </c>
       <c r="F25" s="15">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="G25" s="15">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H25" s="14">
-        <v>-30.597014925373</v>
+        <v>-40.875912408759</v>
       </c>
       <c r="I25" s="15">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="J25" s="15">
-        <v>440</v>
+        <v>509</v>
       </c>
       <c r="K25" s="14">
-        <v>-20.681818181818</v>
+        <v>-26.326129666011</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.629856850715</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>-27.027027027027</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I26" s="15">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J26" s="15">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K26" s="14">
-        <v>-33.898305084745</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="L26" s="14">
-        <v>-15.217391304347</v>
+        <v>6</v>
       </c>
       <c r="M26" s="14">
-        <v>34.482758620689</v>
+        <v>55.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>-42.857142857142</v>
+        <v>-62.5</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="L28" s="14">
-        <v>11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -884,8 +884,8 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-44.444444444444</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I16" s="15">
         <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>33.333333333333</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="14">
         <v>150</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.815602836879</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>133.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>111.111111111111</v>
+        <v>90.909090909090</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14">
-        <v>153.846153846154</v>
+        <v>129.411764705882</v>
       </c>
       <c r="L17" s="14">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="M17" s="14">
-        <v>266.666666666667</v>
+        <v>290</v>
       </c>
       <c r="N17" s="14">
-        <v>37.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-35.714285714285</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>-24</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L18" s="14">
-        <v>-45.714285714285</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-44.117647058823</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.677419354838</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E19" s="14">
-        <v>-18.75</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="F19" s="15">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G19" s="15">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H19" s="14">
-        <v>-7.608695652173</v>
+        <v>-31.132075471698</v>
       </c>
       <c r="I19" s="15">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J19" s="15">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.906976744186</v>
+        <v>-11.442786069651</v>
       </c>
       <c r="L19" s="14">
-        <v>17.605633802816</v>
+        <v>5.952380952380</v>
       </c>
       <c r="M19" s="14">
-        <v>9.868421052631</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.424430641821</v>
+        <v>-67.458866544789</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L20" s="14">
         <v>100</v>
@@ -1131,7 +1131,7 @@
         <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.620437956204</v>
+        <v>-96.103896103896</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>-46.341463414634</v>
       </c>
       <c r="F21" s="17">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G21" s="17">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.651162790697</v>
+        <v>-23.841059602649</v>
       </c>
       <c r="I21" s="17">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="J21" s="17">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>5.150214592274</v>
+        <v>-2.554744525547</v>
       </c>
       <c r="L21" s="18">
-        <v>8.888888888888</v>
+        <v>-1.476014760147</v>
       </c>
       <c r="M21" s="18">
-        <v>19.512195121951</v>
+        <v>13.135593220339</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.076923076923</v>
+        <v>-74.277456647398</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,22 +1192,22 @@
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H22" s="14">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="14">
+        <v>-78.571428571428</v>
+      </c>
+      <c r="L22" s="14">
         <v>-75</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-70</v>
       </c>
       <c r="M22" s="14">
         <v>-76.923076923076</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>-38.157894736842</v>
       </c>
       <c r="F24" s="15">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G24" s="15">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.531135531135</v>
+        <v>-37.024221453287</v>
       </c>
       <c r="I24" s="15">
-        <v>375</v>
+        <v>422</v>
       </c>
       <c r="J24" s="15">
-        <v>513</v>
+        <v>589</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.900584795321</v>
+        <v>-28.353140916808</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.440559440559</v>
+        <v>-36.731634182908</v>
       </c>
       <c r="M24" s="14">
-        <v>80.288461538461</v>
+        <v>84.279475982532</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D25" s="15">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E25" s="14">
-        <v>-62.318840579710</v>
+        <v>-44.578313253012</v>
       </c>
       <c r="F25" s="15">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G25" s="15">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="H25" s="14">
-        <v>-40.875912408759</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="J25" s="15">
-        <v>509</v>
+        <v>592</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.326129666011</v>
+        <v>-28.885135135135</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.782608695652</v>
+        <v>-36.691729323308</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>16.129032258064</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J26" s="15">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.461538461538</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="L26" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>55.882352941176</v>
+        <v>65.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>25</v>
       </c>
       <c r="L28" s="14">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="15">
         <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="15">
-        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -904,11 +904,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>-73.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.761904761904</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L16" s="14">
-        <v>-20</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M16" s="14">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-87.790697674418</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>90.909090909090</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K17" s="14">
-        <v>129.411764705882</v>
+        <v>115</v>
       </c>
       <c r="L17" s="14">
-        <v>56</v>
+        <v>65.384615384615</v>
       </c>
       <c r="M17" s="14">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="N17" s="14">
-        <v>56</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-7.692307692307</v>
+        <v>50</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14">
-        <v>-7.692307692307</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L18" s="14">
-        <v>-46.666666666666</v>
+        <v>-45.098039215686</v>
       </c>
       <c r="M18" s="14">
-        <v>-36.842105263157</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.333333333333</v>
+        <v>-83.030303030303</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D19" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="14">
-        <v>-62.068965517241</v>
+        <v>-18.75</v>
       </c>
       <c r="F19" s="15">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" s="15">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H19" s="14">
-        <v>-31.132075471698</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="I19" s="15">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="J19" s="15">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.442786069651</v>
+        <v>-12.875536480686</v>
       </c>
       <c r="L19" s="14">
-        <v>5.952380952380</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>4.639175257731</v>
       </c>
       <c r="N19" s="14">
-        <v>-67.458866544789</v>
+        <v>-66.775777414075</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,22 +1107,22 @@
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
         <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L20" s="14">
         <v>100</v>
@@ -1131,7 +1131,7 @@
         <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.103896103896</v>
+        <v>-96.470588235294</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
         <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.341463414634</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="F21" s="17">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" s="17">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.841059602649</v>
+        <v>-21.088435374149</v>
       </c>
       <c r="I21" s="17">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.554744525547</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.476014760147</v>
+        <v>0.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>13.135593220339</v>
+        <v>17.120622568093</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.277456647398</v>
+        <v>-74.006908462867</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H22" s="14">
-        <v>-90</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K22" s="14">
-        <v>-78.571428571428</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="L22" s="14">
-        <v>-75</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M22" s="14">
-        <v>-76.923076923076</v>
+        <v>-68.75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D24" s="15">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.157894736842</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="F24" s="15">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G24" s="15">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="H24" s="14">
-        <v>-37.024221453287</v>
+        <v>-37.992831541218</v>
       </c>
       <c r="I24" s="15">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="J24" s="15">
-        <v>589</v>
+        <v>647</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.353140916808</v>
+        <v>-28.438948995363</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.731634182908</v>
+        <v>-38.430851063829</v>
       </c>
       <c r="M24" s="14">
-        <v>84.279475982532</v>
+        <v>74.716981132075</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D25" s="15">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="E25" s="14">
-        <v>-44.578313253012</v>
+        <v>-35</v>
       </c>
       <c r="F25" s="15">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G25" s="15">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H25" s="14">
-        <v>-43.333333333333</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I25" s="15">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="J25" s="15">
-        <v>592</v>
+        <v>652</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.885135135135</v>
+        <v>-29.447852760736</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.691729323308</v>
+        <v>-38.829787234042</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>150</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>41.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J26" s="15">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.432835820895</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M26" s="14">
-        <v>65.714285714285</v>
+        <v>65</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
-        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
+        <v>11</v>
+      </c>
+      <c r="J28" s="15">
         <v>10</v>
       </c>
-      <c r="J28" s="15">
-        <v>8</v>
-      </c>
       <c r="K28" s="14">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,13 +1570,13 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>-75</v>
+      </c>
+      <c r="L31" s="14">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-75</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="14">
-        <v>-8.695652173913</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-19.230769230769</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M16" s="14">
-        <v>133.333333333333</v>
+        <v>130</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.790697674418</v>
+        <v>-88.144329896907</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I17" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="L17" s="14">
-        <v>65.384615384615</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M17" s="14">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="N17" s="14">
-        <v>34.375</v>
+        <v>29.729729729729</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>50</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I18" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K18" s="14">
-        <v>-3.448275862068</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="L18" s="14">
-        <v>-45.098039215686</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-33.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.030303030303</v>
+        <v>-81.767955801105</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D19" s="15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="14">
-        <v>-18.75</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F19" s="15">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G19" s="15">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H19" s="14">
-        <v>-32.727272727272</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="I19" s="15">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="J19" s="15">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="K19" s="14">
-        <v>-12.875536480686</v>
+        <v>-14.122137404580</v>
       </c>
       <c r="L19" s="14">
-        <v>7.407407407407</v>
+        <v>6.132075471698</v>
       </c>
       <c r="M19" s="14">
-        <v>4.639175257731</v>
+        <v>3.211009174311</v>
       </c>
       <c r="N19" s="14">
-        <v>-66.775777414075</v>
+        <v>-66.114457831325</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L20" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.470588235294</v>
+        <v>-96.195652173913</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.951219512195</v>
+        <v>-15</v>
       </c>
       <c r="F21" s="17">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G21" s="17">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.088435374149</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="I21" s="17">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="J21" s="17">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.444444444444</v>
+        <v>-5.352112676056</v>
       </c>
       <c r="L21" s="18">
-        <v>0.333333333333</v>
+        <v>1.818181818181</v>
       </c>
       <c r="M21" s="18">
-        <v>17.120622568093</v>
+        <v>17.894736842105</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.006908462867</v>
+        <v>-73.501577287066</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="14">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="15">
         <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="14">
-        <v>-75</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K22" s="14">
-        <v>-73.684210526315</v>
+        <v>-73.913043478260</v>
       </c>
       <c r="L22" s="14">
-        <v>-61.538461538461</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M22" s="14">
-        <v>-68.75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="15">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E24" s="14">
-        <v>-29.310344827586</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="F24" s="15">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G24" s="15">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H24" s="14">
-        <v>-37.992831541218</v>
+        <v>-40.441176470588</v>
       </c>
       <c r="I24" s="15">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="J24" s="15">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.438948995363</v>
+        <v>-29.733520336605</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.430851063829</v>
+        <v>-39.346246973365</v>
       </c>
       <c r="M24" s="14">
-        <v>74.716981132075</v>
+        <v>70.408163265306</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D25" s="15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E25" s="14">
-        <v>-35</v>
+        <v>-46.969696969697</v>
       </c>
       <c r="F25" s="15">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G25" s="15">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="H25" s="14">
-        <v>-44.827586206896</v>
+        <v>-47.841726618705</v>
       </c>
       <c r="I25" s="15">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="J25" s="15">
-        <v>652</v>
+        <v>718</v>
       </c>
       <c r="K25" s="14">
-        <v>-29.447852760736</v>
+        <v>-31.197771587743</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.829787234042</v>
+        <v>-40.338164251207</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>16.666666666666</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J26" s="15">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.455696202531</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.347826086956</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="M26" s="14">
-        <v>65</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>5</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>-87.5</v>
       </c>
       <c r="I28" s="15">
         <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>10</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-42.105263157894</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="15">
         <v>1</v>
       </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
         <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,26 +895,26 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
         <v>-100</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
         <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-63.636363636363</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I16" s="15">
         <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.166666666666</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L16" s="14">
-        <v>-14.814814814814</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M16" s="14">
         <v>130</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.144329896907</v>
+        <v>-89.150943396226</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>42.857142857142</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I17" s="15">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>100</v>
+        <v>96.153846153846</v>
       </c>
       <c r="L17" s="14">
-        <v>71.428571428571</v>
+        <v>59.375</v>
       </c>
       <c r="M17" s="14">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="N17" s="14">
-        <v>29.729729729729</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>19</v>
@@ -1034,22 +1034,22 @@
         <v>46.153846153846</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J18" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>-5.714285714285</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.888888888888</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="M18" s="14">
-        <v>-21.428571428571</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.767955801105</v>
+        <v>-80.104712041884</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D19" s="15">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E19" s="14">
-        <v>-20.689655172413</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F19" s="15">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G19" s="15">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H19" s="14">
-        <v>-32.075471698113</v>
+        <v>-16.964285714285</v>
       </c>
       <c r="I19" s="15">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="J19" s="15">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="K19" s="14">
-        <v>-14.122137404580</v>
+        <v>-8.450704225352</v>
       </c>
       <c r="L19" s="14">
-        <v>6.132075471698</v>
+        <v>7.883817427385</v>
       </c>
       <c r="M19" s="14">
-        <v>3.211009174311</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N19" s="14">
-        <v>-66.114457831325</v>
+        <v>-64.529331514324</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>50</v>
       </c>
       <c r="I20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L20" s="14">
-        <v>133.333333333333</v>
+        <v>80</v>
       </c>
       <c r="M20" s="14">
-        <v>133.333333333333</v>
+        <v>125</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.195652173913</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-15</v>
+        <v>38.709677419354</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.178082191780</v>
+        <v>-13.071895424836</v>
       </c>
       <c r="I21" s="17">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="J21" s="17">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.352112676056</v>
+        <v>-1.295336787564</v>
       </c>
       <c r="L21" s="18">
-        <v>1.818181818181</v>
+        <v>3.532608695652</v>
       </c>
       <c r="M21" s="18">
-        <v>17.894736842105</v>
+        <v>25.742574257425</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.501577287066</v>
+        <v>-72.431259044862</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="15">
         <v>4</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F22" s="15">
-        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>13</v>
       </c>
       <c r="H22" s="14">
-        <v>-76.923076923076</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K22" s="14">
-        <v>-73.913043478260</v>
+        <v>-68</v>
       </c>
       <c r="L22" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E24" s="14">
-        <v>-39.393939393939</v>
+        <v>-40.506329113924</v>
       </c>
       <c r="F24" s="15">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G24" s="15">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.441176470588</v>
+        <v>-38.351254480286</v>
       </c>
       <c r="I24" s="15">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="J24" s="15">
-        <v>713</v>
+        <v>792</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.733520336605</v>
+        <v>-31.060606060606</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.346246973365</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M24" s="14">
-        <v>70.408163265306</v>
+        <v>65.454545454545</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D25" s="15">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E25" s="14">
-        <v>-46.969696969697</v>
+        <v>-42.028985507246</v>
       </c>
       <c r="F25" s="15">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="G25" s="15">
         <v>278</v>
       </c>
       <c r="H25" s="14">
-        <v>-47.841726618705</v>
+        <v>-43.165467625899</v>
       </c>
       <c r="I25" s="15">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="J25" s="15">
-        <v>718</v>
+        <v>787</v>
       </c>
       <c r="K25" s="14">
-        <v>-31.197771587743</v>
+        <v>-32.274459974587</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.338164251207</v>
+        <v>-41.234840132304</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.448275862068</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="J26" s="15">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="K26" s="14">
-        <v>-22.727272727272</v>
+        <v>-15.841584158415</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.049382716049</v>
+        <v>-7.608695652173</v>
       </c>
       <c r="M26" s="14">
-        <v>33.333333333333</v>
+        <v>60.377358490566</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>5</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-87.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
         <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-26.666666666666</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-50</v>
+        <v>-44</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
@@ -1576,7 +1576,7 @@
         <v>-50</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-72.727272727272</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>-11.538461538461</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L16" s="14">
-        <v>-17.857142857142</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M16" s="14">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.150943396226</v>
+        <v>-89.787234042553</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>15.384615384615</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>96.153846153846</v>
+        <v>79.310344827586</v>
       </c>
       <c r="L17" s="14">
-        <v>59.375</v>
+        <v>26.829268292682</v>
       </c>
       <c r="M17" s="14">
-        <v>325</v>
+        <v>333.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>27.5</v>
+        <v>15.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
-      </c>
-      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="14">
-        <v>66.666666666666</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>46.153846153846</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J18" s="15">
         <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>7.894736842105</v>
       </c>
       <c r="L18" s="14">
-        <v>-32.142857142857</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="M18" s="14">
-        <v>-11.627906976744</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.104712041884</v>
+        <v>-80.841121495327</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D19" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="14">
-        <v>54.545454545454</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F19" s="15">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G19" s="15">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H19" s="14">
-        <v>-16.964285714285</v>
+        <v>-4.587155963302</v>
       </c>
       <c r="I19" s="15">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="J19" s="15">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.450704225352</v>
+        <v>-9.032258064516</v>
       </c>
       <c r="L19" s="14">
-        <v>7.883817427385</v>
+        <v>9.302325581395</v>
       </c>
       <c r="M19" s="14">
-        <v>11.111111111111</v>
+        <v>9.727626459143</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.529331514324</v>
+        <v>-65.313653136531</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="14">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="M20" s="14">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.454545454545</v>
+        <v>-94.711538461538</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>38.709677419354</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G21" s="17">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.071895424836</v>
+        <v>-7.382550335570</v>
       </c>
       <c r="I21" s="17">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="J21" s="17">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.295336787564</v>
+        <v>-3.073286052009</v>
       </c>
       <c r="L21" s="18">
-        <v>3.532608695652</v>
+        <v>1.736972704714</v>
       </c>
       <c r="M21" s="18">
-        <v>25.742574257425</v>
+        <v>22.754491017964</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.431259044862</v>
+        <v>-73.079448456992</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H22" s="14">
-        <v>-69.230769230769</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K22" s="14">
-        <v>-68</v>
+        <v>-68.965517241379</v>
       </c>
       <c r="L22" s="14">
         <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-55.555555555555</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D24" s="15">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E24" s="14">
-        <v>-40.506329113924</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="F24" s="15">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G24" s="15">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.351254480286</v>
+        <v>-34.558823529411</v>
       </c>
       <c r="I24" s="15">
-        <v>546</v>
+        <v>597</v>
       </c>
       <c r="J24" s="15">
-        <v>792</v>
+        <v>861</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.060606060606</v>
+        <v>-30.662020905923</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.534883720930</v>
+        <v>-39.574898785425</v>
       </c>
       <c r="M24" s="14">
-        <v>65.454545454545</v>
+        <v>63.561643835616</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D25" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E25" s="14">
-        <v>-42.028985507246</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="15">
         <v>158</v>
       </c>
       <c r="G25" s="15">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="H25" s="14">
-        <v>-43.165467625899</v>
+        <v>-40.823970037453</v>
       </c>
       <c r="I25" s="15">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="J25" s="15">
-        <v>787</v>
+        <v>859</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.274459974587</v>
+        <v>-32.712456344586</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.234840132304</v>
+        <v>-41.319796954314</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>30.769230769230</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H26" s="14">
-        <v>-8.333333333333</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="I26" s="15">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J26" s="15">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.841584158415</v>
+        <v>-19.827586206896</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.608695652173</v>
+        <v>-7.920792079207</v>
       </c>
       <c r="M26" s="14">
-        <v>60.377358490566</v>
+        <v>57.627118644067</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>-6.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I15" s="15">
+        <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
       <c r="L15" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
+        <v>6</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="F16" s="15">
         <v>5</v>
       </c>
-      <c r="E16" s="14">
-        <v>-80</v>
-      </c>
-      <c r="F16" s="15">
-        <v>4</v>
-      </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-60</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K16" s="14">
-        <v>-22.580645161290</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="L16" s="14">
-        <v>-22.580645161290</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M16" s="14">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.787234042553</v>
+        <v>-89.84375</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-25</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>79.310344827586</v>
+        <v>65.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>26.829268292682</v>
+        <v>38.095238095238</v>
       </c>
       <c r="M17" s="14">
-        <v>333.333333333333</v>
+        <v>383.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>15.555555555555</v>
+        <v>23.404255319148</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>8</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-87.5</v>
       </c>
       <c r="F18" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I18" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K18" s="14">
-        <v>7.894736842105</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L18" s="14">
-        <v>-30.508474576271</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-16.326530612244</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.841121495327</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D19" s="15">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E19" s="14">
-        <v>-15.384615384615</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G19" s="15">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H19" s="14">
-        <v>-4.587155963302</v>
+        <v>11.340206185567</v>
       </c>
       <c r="I19" s="15">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="J19" s="15">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.032258064516</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="L19" s="14">
-        <v>9.302325581395</v>
+        <v>12.318840579710</v>
       </c>
       <c r="M19" s="14">
-        <v>9.727626459143</v>
+        <v>14.814814814814</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.313653136531</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>37.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L20" s="14">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="M20" s="14">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.711538461538</v>
+        <v>-93.777777777777</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.621621621621</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="G21" s="17">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.382550335570</v>
+        <v>-1.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="J21" s="17">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.073286052009</v>
+        <v>-3.010752688172</v>
       </c>
       <c r="L21" s="18">
-        <v>1.736972704714</v>
+        <v>5.868544600938</v>
       </c>
       <c r="M21" s="18">
-        <v>22.754491017964</v>
+        <v>27.762039660056</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.079448456992</v>
+        <v>-72.382118799755</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I22" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J22" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K22" s="14">
-        <v>-68.965517241379</v>
+        <v>-62.5</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-52.631578947368</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D24" s="15">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E24" s="14">
-        <v>-26.086956521739</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G24" s="15">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.558823529411</v>
+        <v>-32.846715328467</v>
       </c>
       <c r="I24" s="15">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="J24" s="15">
-        <v>861</v>
+        <v>921</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.662020905923</v>
+        <v>-30.184581976112</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.574898785425</v>
+        <v>-38.761904761904</v>
       </c>
       <c r="M24" s="14">
-        <v>63.561643835616</v>
+        <v>60.349127182044</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" s="15">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E25" s="14">
-        <v>-37.5</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="F25" s="15">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G25" s="15">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H25" s="14">
-        <v>-40.823970037453</v>
+        <v>-37.692307692307</v>
       </c>
       <c r="I25" s="15">
-        <v>578</v>
+        <v>620</v>
       </c>
       <c r="J25" s="15">
-        <v>859</v>
+        <v>912</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.712456344586</v>
+        <v>-32.017543859649</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.319796954314</v>
+        <v>-40.726577437858</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>-46.666666666666</v>
+        <v>40</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>-26.530612244898</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J26" s="15">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K26" s="14">
-        <v>-19.827586206896</v>
+        <v>-17.355371900826</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.920792079207</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M26" s="14">
-        <v>57.627118644067</v>
+        <v>58.730158730158</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>-75</v>
+      </c>
+      <c r="I27" s="15">
+        <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="14">
-        <v>-100</v>
+        <v>-90</v>
       </c>
       <c r="L27" s="14">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I28" s="15">
         <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K28" s="14">
-        <v>-16.666666666666</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="L28" s="14">
         <v>-40</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
+        <v>-80</v>
+      </c>
+      <c r="L31" s="14">
         <v>-50</v>
-      </c>
-      <c r="L31" s="14">
-        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -934,81 +934,81 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
         <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>-83.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H16" s="14">
-        <v>-64.285714285714</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J16" s="15">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K16" s="14">
-        <v>-29.729729729729</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="L16" s="14">
-        <v>-16.129032258064</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>85.714285714285</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.84375</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-13.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="15">
         <v>58</v>
       </c>
       <c r="J17" s="15">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K17" s="14">
-        <v>65.714285714285</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L17" s="14">
-        <v>38.095238095238</v>
+        <v>26.086956521739</v>
       </c>
       <c r="M17" s="14">
-        <v>383.333333333333</v>
+        <v>314.285714285714</v>
       </c>
       <c r="N17" s="14">
-        <v>23.404255319148</v>
+        <v>11.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-87.5</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-23.529411764705</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J18" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
-        <v>-8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-33.333333333333</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="M18" s="14">
-        <v>-20.754716981132</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.578947368421</v>
+        <v>-79.674796747967</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F19" s="15">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" s="15">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="H19" s="14">
-        <v>11.340206185567</v>
+        <v>22.471910112359</v>
       </c>
       <c r="I19" s="15">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="J19" s="15">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.060606060606</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L19" s="14">
-        <v>12.318840579710</v>
+        <v>12.5</v>
       </c>
       <c r="M19" s="14">
-        <v>14.814814814814</v>
+        <v>9.180327868852</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.285714285714</v>
+        <v>-64.461045891141</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>55.555555555555</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L20" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M20" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.777777777777</v>
+        <v>-93.277310924369</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-7.5</v>
       </c>
       <c r="F21" s="17">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G21" s="17">
         <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.333333333333</v>
+        <v>2</v>
       </c>
       <c r="I21" s="17">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="J21" s="17">
-        <v>465</v>
+        <v>505</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.010752688172</v>
+        <v>-2.772277227722</v>
       </c>
       <c r="L21" s="18">
-        <v>5.868544600938</v>
+        <v>6.971677559912</v>
       </c>
       <c r="M21" s="18">
-        <v>27.762039660056</v>
+        <v>23.366834170854</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.382118799755</v>
+        <v>-71.878579610538</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" s="14">
-        <v>0</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F22" s="15">
         <v>6</v>
       </c>
       <c r="G22" s="15">
+        <v>15</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-60</v>
+      </c>
+      <c r="I22" s="15">
         <v>13</v>
       </c>
-      <c r="H22" s="14">
-        <v>-53.846153846153</v>
-      </c>
-      <c r="I22" s="15">
-        <v>12</v>
-      </c>
       <c r="J22" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K22" s="14">
-        <v>-62.5</v>
+        <v>-65.789473684210</v>
       </c>
       <c r="L22" s="14">
-        <v>-33.333333333333</v>
+        <v>-35</v>
       </c>
       <c r="M22" s="14">
-        <v>-36.842105263157</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D24" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E24" s="14">
-        <v>-23.333333333333</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="F24" s="15">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G24" s="15">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.846715328467</v>
+        <v>-26.373626373626</v>
       </c>
       <c r="I24" s="15">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="J24" s="15">
-        <v>921</v>
+        <v>986</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.184581976112</v>
+        <v>-29.107505070993</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.761904761904</v>
+        <v>-38.791593695271</v>
       </c>
       <c r="M24" s="14">
-        <v>60.349127182044</v>
+        <v>60.689655172413</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D25" s="15">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E25" s="14">
-        <v>-20.754716981132</v>
+        <v>-7.8125</v>
       </c>
       <c r="F25" s="15">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="G25" s="15">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H25" s="14">
-        <v>-37.692307692307</v>
+        <v>-28.294573643410</v>
       </c>
       <c r="I25" s="15">
-        <v>620</v>
+        <v>677</v>
       </c>
       <c r="J25" s="15">
-        <v>912</v>
+        <v>976</v>
       </c>
       <c r="K25" s="14">
-        <v>-32.017543859649</v>
+        <v>-30.635245901639</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.726577437858</v>
+        <v>-40.352422907489</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G26" s="15">
         <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>-16.666666666666</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="15">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J26" s="15">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K26" s="14">
-        <v>-17.355371900826</v>
+        <v>-13.846153846153</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.714285714285</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="M26" s="14">
-        <v>58.730158730158</v>
+        <v>69.696969696969</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1406,10 +1406,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="14">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="L27" s="14">
         <v>-83.333333333333</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-69.230769230769</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J28" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K28" s="14">
-        <v>-34.782608695652</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>-40</v>
+        <v>-28</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>-80</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="L15" s="14">
         <v>-80</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,81 +934,81 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>16.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-47.368421052631</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I16" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K16" s="14">
-        <v>-23.255813953488</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M16" s="14">
-        <v>83.333333333333</v>
+        <v>76.190476190476</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-86.446886446886</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
         <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>38.095238095238</v>
+        <v>47.727272727272</v>
       </c>
       <c r="L17" s="14">
-        <v>26.086956521739</v>
+        <v>32.653061224489</v>
       </c>
       <c r="M17" s="14">
-        <v>314.285714285714</v>
+        <v>306.25</v>
       </c>
       <c r="N17" s="14">
-        <v>11.538461538461</v>
+        <v>18.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L18" s="14">
-        <v>-26.470588235294</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="M18" s="14">
-        <v>-12.280701754386</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.674796747967</v>
+        <v>-79.310344827586</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D19" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="14">
-        <v>19.047619047619</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F19" s="15">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G19" s="15">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H19" s="14">
-        <v>22.471910112359</v>
+        <v>8.888888888888</v>
       </c>
       <c r="I19" s="15">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="J19" s="15">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.128205128205</v>
+        <v>-5.080213903743</v>
       </c>
       <c r="L19" s="14">
-        <v>12.5</v>
+        <v>12.341772151898</v>
       </c>
       <c r="M19" s="14">
-        <v>9.180327868852</v>
+        <v>9.907120743034</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.461045891141</v>
+        <v>-64.816650148662</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>45.454545454545</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M20" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.277310924369</v>
+        <v>-93.280632411067</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
+        <v>146</v>
+      </c>
+      <c r="G21" s="17">
         <v>153</v>
       </c>
-      <c r="G21" s="17">
-        <v>150</v>
-      </c>
       <c r="H21" s="18">
-        <v>2</v>
+        <v>-4.575163398692</v>
       </c>
       <c r="I21" s="17">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="J21" s="17">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.772277227722</v>
+        <v>-1.855287569573</v>
       </c>
       <c r="L21" s="18">
-        <v>6.971677559912</v>
+        <v>9.072164948453</v>
       </c>
       <c r="M21" s="18">
-        <v>23.366834170854</v>
+        <v>24.178403755868</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.878579610538</v>
+        <v>-71.574422353573</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>6</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-83.333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>6</v>
       </c>
       <c r="G22" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H22" s="14">
-        <v>-60</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I22" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="15">
         <v>38</v>
       </c>
       <c r="K22" s="14">
-        <v>-65.789473684210</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="L22" s="14">
-        <v>-35</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-43.478260869565</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D24" s="15">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E24" s="14">
-        <v>-9.230769230769</v>
+        <v>14.545454545454</v>
       </c>
       <c r="F24" s="15">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="G24" s="15">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="H24" s="14">
-        <v>-26.373626373626</v>
+        <v>-12.85140562249</v>
       </c>
       <c r="I24" s="15">
-        <v>699</v>
+        <v>762</v>
       </c>
       <c r="J24" s="15">
-        <v>986</v>
+        <v>1041</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.107505070993</v>
+        <v>-26.801152737752</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.791593695271</v>
+        <v>-37.335526315789</v>
       </c>
       <c r="M24" s="14">
-        <v>60.689655172413</v>
+        <v>61.099365750528</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D25" s="15">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E25" s="14">
-        <v>-7.8125</v>
+        <v>20.454545454545</v>
       </c>
       <c r="F25" s="15">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G25" s="15">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="H25" s="14">
-        <v>-28.294573643410</v>
+        <v>-14.592274678111</v>
       </c>
       <c r="I25" s="15">
-        <v>677</v>
+        <v>731</v>
       </c>
       <c r="J25" s="15">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.635245901639</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.352422907489</v>
+        <v>-39.636663914120</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>4.761904761904</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I26" s="15">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J26" s="15">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.846153846153</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="L26" s="14">
-        <v>-8.196721311475</v>
+        <v>-13.868613138686</v>
       </c>
       <c r="M26" s="14">
-        <v>69.696969696969</v>
+        <v>68.571428571428</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="14">
-        <v>-90.909090909090</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
-      </c>
-      <c r="D28" s="15">
         <v>4</v>
       </c>
-      <c r="E28" s="14">
-        <v>-25</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
         <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15">
         <v>27</v>
       </c>
       <c r="K28" s="14">
-        <v>-33.333333333333</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L28" s="14">
-        <v>-28</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>-80</v>
       </c>
       <c r="L31" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -920,7 +920,7 @@
         <v>-88.888888888888</v>
       </c>
       <c r="L15" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>300</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
         <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-27.777777777777</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J16" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K16" s="14">
-        <v>-15.909090909090</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="L16" s="14">
-        <v>2.777777777777</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M16" s="14">
-        <v>76.190476190476</v>
+        <v>90.476190476190</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.446886446886</v>
+        <v>-86.013986013986</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="I17" s="15">
         <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>47.727272727272</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L17" s="14">
-        <v>32.653061224489</v>
+        <v>30</v>
       </c>
       <c r="M17" s="14">
-        <v>306.25</v>
+        <v>282.352941176471</v>
       </c>
       <c r="N17" s="14">
-        <v>18.181818181818</v>
+        <v>16.071428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>-22.222222222222</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I18" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J18" s="15">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K18" s="14">
-        <v>-3.571428571428</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-20.588235294117</v>
+        <v>-18.309859154929</v>
       </c>
       <c r="M18" s="14">
-        <v>-11.475409836065</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.310344827586</v>
+        <v>-79.061371841155</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
-        <v>-13.043478260869</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F19" s="15">
         <v>98</v>
       </c>
       <c r="G19" s="15">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H19" s="14">
-        <v>8.888888888888</v>
+        <v>18.072289156626</v>
       </c>
       <c r="I19" s="15">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="J19" s="15">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.080213903743</v>
+        <v>-3.816793893129</v>
       </c>
       <c r="L19" s="14">
-        <v>12.341772151898</v>
+        <v>14.545454545454</v>
       </c>
       <c r="M19" s="14">
-        <v>9.907120743034</v>
+        <v>9.883720930232</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.816650148662</v>
+        <v>-65.096952908587</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>14.285714285714</v>
+        <v>40</v>
       </c>
       <c r="I20" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>41.666666666666</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L20" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M20" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.280632411067</v>
+        <v>-93.233082706766</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>3.333333333333</v>
       </c>
       <c r="F21" s="17">
         <v>146</v>
       </c>
       <c r="G21" s="17">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.575163398692</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="J21" s="17">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.855287569573</v>
+        <v>-1.581722319859</v>
       </c>
       <c r="L21" s="18">
-        <v>9.072164948453</v>
+        <v>10.453648915187</v>
       </c>
       <c r="M21" s="18">
-        <v>24.178403755868</v>
+        <v>24.168514412416</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.574422353573</v>
+        <v>-71.688574317492</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H22" s="14">
-        <v>-53.846153846153</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I22" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K22" s="14">
-        <v>-63.157894736842</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="14">
-        <v>-33.333333333333</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M22" s="14">
-        <v>-39.130434782608</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D24" s="15">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E24" s="14">
-        <v>14.545454545454</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="F24" s="15">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="G24" s="15">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H24" s="14">
-        <v>-12.85140562249</v>
+        <v>-5.976095617529</v>
       </c>
       <c r="I24" s="15">
-        <v>762</v>
+        <v>831</v>
       </c>
       <c r="J24" s="15">
-        <v>1041</v>
+        <v>1112</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.801152737752</v>
+        <v>-25.269784172661</v>
       </c>
       <c r="L24" s="14">
-        <v>-37.335526315789</v>
+        <v>-36.757990867579</v>
       </c>
       <c r="M24" s="14">
-        <v>61.099365750528</v>
+        <v>62.622309197651</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D25" s="15">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="E25" s="14">
-        <v>20.454545454545</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="F25" s="15">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G25" s="15">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H25" s="14">
-        <v>-14.592274678111</v>
+        <v>-7.359307359307</v>
       </c>
       <c r="I25" s="15">
-        <v>731</v>
+        <v>790</v>
       </c>
       <c r="J25" s="15">
-        <v>1020</v>
+        <v>1090</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.333333333333</v>
+        <v>-27.522935779816</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.636663914120</v>
+        <v>-39.694656488549</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="15">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>-20.930232558139</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I26" s="15">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J26" s="15">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.055555555555</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.868613138686</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M26" s="14">
-        <v>68.571428571428</v>
+        <v>65.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>6</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-83.333333333333</v>
       </c>
       <c r="F28" s="15">
         <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K28" s="14">
-        <v>-18.518518518518</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="L28" s="14">
-        <v>-24.137931034482</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1567,16 +1567,16 @@
         <v>-100</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="L31" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I15" s="15">
-        <v>1</v>
       </c>
       <c r="J15" s="15">
         <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>-88.888888888888</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="L15" s="14">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J16" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="14">
-        <v>-18.367346938775</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="L16" s="14">
-        <v>2.564102564102</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="M16" s="14">
-        <v>90.476190476190</v>
+        <v>100</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.013986013986</v>
+        <v>-85.906040268456</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>-31.25</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J17" s="15">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K17" s="14">
-        <v>44.444444444444</v>
+        <v>34.693877551020</v>
       </c>
       <c r="L17" s="14">
-        <v>30</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M17" s="14">
-        <v>282.352941176471</v>
+        <v>230</v>
       </c>
       <c r="N17" s="14">
-        <v>16.071428571428</v>
+        <v>13.793103448275</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>-36.363636363636</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J18" s="15">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K18" s="14">
-        <v>-3.333333333333</v>
+        <v>-3.125</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.309859154929</v>
+        <v>-19.480519480519</v>
       </c>
       <c r="M18" s="14">
-        <v>-7.936507936507</v>
+        <v>-4.615384615384</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.061371841155</v>
+        <v>-78.839590443686</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E19" s="14">
-        <v>15.789473684210</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F19" s="15">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="G19" s="15">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="14">
-        <v>18.072289156626</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="I19" s="15">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="J19" s="15">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.816793893129</v>
+        <v>-6.280193236714</v>
       </c>
       <c r="L19" s="14">
-        <v>14.545454545454</v>
+        <v>6.887052341597</v>
       </c>
       <c r="M19" s="14">
-        <v>9.883720930232</v>
+        <v>7.182320441988</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.096952908587</v>
+        <v>-66.406926406926</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J20" s="15">
         <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>38.461538461538</v>
+        <v>76.923076923076</v>
       </c>
       <c r="L20" s="14">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>187.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.233082706766</v>
+        <v>-91.98606271777</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>3.333333333333</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-8.029197080291</v>
       </c>
       <c r="I21" s="17">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="J21" s="17">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.581722319859</v>
+        <v>-3.156146179401</v>
       </c>
       <c r="L21" s="18">
-        <v>10.453648915187</v>
+        <v>4.293381037567</v>
       </c>
       <c r="M21" s="18">
-        <v>24.168514412416</v>
+        <v>22.478991596638</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.688574317492</v>
+        <v>-72.264509990485</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H22" s="14">
-        <v>-36.363636363636</v>
+        <v>-12.5</v>
       </c>
       <c r="I22" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J22" s="15">
         <v>40</v>
       </c>
       <c r="K22" s="14">
-        <v>-60</v>
+        <v>-52.5</v>
       </c>
       <c r="L22" s="14">
-        <v>-30.434782608695</v>
+        <v>-24</v>
       </c>
       <c r="M22" s="14">
-        <v>-30.434782608695</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D24" s="15">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E24" s="14">
-        <v>-5.633802816901</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="F24" s="15">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G24" s="15">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H24" s="14">
-        <v>-5.976095617529</v>
+        <v>-1.190476190476</v>
       </c>
       <c r="I24" s="15">
-        <v>831</v>
+        <v>889</v>
       </c>
       <c r="J24" s="15">
-        <v>1112</v>
+        <v>1173</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.269784172661</v>
+        <v>-24.211423699914</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.757990867579</v>
+        <v>-35.951008645533</v>
       </c>
       <c r="M24" s="14">
-        <v>62.622309197651</v>
+        <v>61.636363636363</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D25" s="15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E25" s="14">
-        <v>-17.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="15">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G25" s="15">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H25" s="14">
-        <v>-7.359307359307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I25" s="15">
-        <v>790</v>
+        <v>839</v>
       </c>
       <c r="J25" s="15">
-        <v>1090</v>
+        <v>1150</v>
       </c>
       <c r="K25" s="14">
-        <v>-27.522935779816</v>
+        <v>-27.043478260869</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.694656488549</v>
+        <v>-39.158810732414</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-37.5</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="I26" s="15">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="J26" s="15">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.421052631578</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.888888888888</v>
+        <v>-11.409395973154</v>
       </c>
       <c r="M26" s="14">
-        <v>65.333333333333</v>
+        <v>60.975609756097</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <v>3</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I27" s="15">
-        <v>2</v>
       </c>
       <c r="J27" s="15">
         <v>12</v>
       </c>
       <c r="K27" s="14">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="L27" s="14">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-83.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-46.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>23</v>
       </c>
       <c r="J28" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K28" s="14">
-        <v>-30.303030303030</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L28" s="14">
-        <v>-25.806451612903</v>
+        <v>-28.125</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1570,13 +1570,13 @@
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-001pct.xlsx
+++ b/data/source/weekly/cs-en-us-001pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="L15" s="14">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J16" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K16" s="14">
-        <v>-20.754716981132</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="L16" s="14">
-        <v>-2.325581395348</v>
+        <v>2.272727272727</v>
       </c>
       <c r="M16" s="14">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.906040268456</v>
+        <v>-85.389610389610</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>75</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-57.142857142857</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I17" s="15">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J17" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>34.693877551020</v>
+        <v>37.735849056603</v>
       </c>
       <c r="L17" s="14">
-        <v>13.793103448275</v>
+        <v>17.741935483871</v>
       </c>
       <c r="M17" s="14">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="N17" s="14">
-        <v>13.793103448275</v>
+        <v>21.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I18" s="15">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J18" s="15">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K18" s="14">
-        <v>-3.125</v>
+        <v>-2.739726027397</v>
       </c>
       <c r="L18" s="14">
-        <v>-19.480519480519</v>
+        <v>-11.25</v>
       </c>
       <c r="M18" s="14">
-        <v>-4.615384615384</v>
+        <v>5.970149253731</v>
       </c>
       <c r="N18" s="14">
-        <v>-78.839590443686</v>
+        <v>-77.096774193548</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E19" s="14">
-        <v>-47.619047619047</v>
+        <v>47.058823529411</v>
       </c>
       <c r="F19" s="15">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G19" s="15">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H19" s="14">
-        <v>-5.952380952380</v>
+        <v>-6.25</v>
       </c>
       <c r="I19" s="15">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="J19" s="15">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.280193236714</v>
+        <v>-4.640371229698</v>
       </c>
       <c r="L19" s="14">
-        <v>6.887052341597</v>
+        <v>5.384615384615</v>
       </c>
       <c r="M19" s="14">
-        <v>7.182320441988</v>
+        <v>6.753246753246</v>
       </c>
       <c r="N19" s="14">
-        <v>-66.406926406926</v>
+        <v>-66.144975288303</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>5</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
         <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>76.923076923076</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L20" s="14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M20" s="14">
-        <v>187.5</v>
+        <v>144.444444444444</v>
       </c>
       <c r="N20" s="14">
-        <v>-91.98606271777</v>
+        <v>-92.833876221498</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.242424242424</v>
+        <v>22.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G21" s="17">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.029197080291</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>583</v>
+        <v>624</v>
       </c>
       <c r="J21" s="17">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.156146179401</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L21" s="18">
-        <v>4.293381037567</v>
+        <v>4.697986577181</v>
       </c>
       <c r="M21" s="18">
-        <v>22.478991596638</v>
+        <v>23.564356435643</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.264509990485</v>
+        <v>-71.764705882352</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>100</v>
+      </c>
+      <c r="F22" s="15">
+        <v>9</v>
+      </c>
+      <c r="G22" s="15">
         <v>3</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>7</v>
-      </c>
-      <c r="G22" s="15">
-        <v>8</v>
-      </c>
       <c r="H22" s="14">
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
+        <v>21</v>
+      </c>
+      <c r="J22" s="15">
+        <v>41</v>
+      </c>
+      <c r="K22" s="14">
+        <v>-48.780487804878</v>
+      </c>
+      <c r="L22" s="14">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="M22" s="14">
         <v>-12.5</v>
-      </c>
-      <c r="I22" s="15">
-        <v>19</v>
-      </c>
-      <c r="J22" s="15">
-        <v>40</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-52.5</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-24</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-20.833333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D24" s="15">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="E24" s="14">
-        <v>-6.557377049180</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="F24" s="15">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="G24" s="15">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="H24" s="14">
-        <v>-1.190476190476</v>
+        <v>-12.363636363636</v>
       </c>
       <c r="I24" s="15">
-        <v>889</v>
+        <v>941</v>
       </c>
       <c r="J24" s="15">
-        <v>1173</v>
+        <v>1261</v>
       </c>
       <c r="K24" s="14">
-        <v>-24.211423699914</v>
+        <v>-25.376685170499</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.951008645533</v>
+        <v>-35.724043715847</v>
       </c>
       <c r="M24" s="14">
-        <v>61.636363636363</v>
+        <v>58.952702702702</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D25" s="15">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E25" s="14">
-        <v>-20</v>
+        <v>-42.696629213483</v>
       </c>
       <c r="F25" s="15">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G25" s="15">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="H25" s="14">
-        <v>-7.142857142857</v>
+        <v>-18.250950570342</v>
       </c>
       <c r="I25" s="15">
-        <v>839</v>
+        <v>893</v>
       </c>
       <c r="J25" s="15">
-        <v>1150</v>
+        <v>1239</v>
       </c>
       <c r="K25" s="14">
-        <v>-27.043478260869</v>
+        <v>-27.925746569814</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.158810732414</v>
+        <v>-38.328729281768</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.810810810810</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J26" s="15">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.455696202531</v>
+        <v>-11.875</v>
       </c>
       <c r="L26" s="14">
-        <v>-11.409395973154</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="M26" s="14">
-        <v>60.975609756097</v>
+        <v>63.953488372093</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,10 +1397,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>-75</v>
       </c>
       <c r="L27" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K28" s="14">
-        <v>-34.285714285714</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L28" s="14">
-        <v>-28.125</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
